--- a/artfynd/A 2838-2026 artfynd.xlsx
+++ b/artfynd/A 2838-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>121078567</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,62 +782,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121078807</v>
+        <v>121099286</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagsberget, Middagsberget, Jmt</t>
+          <t>Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507467</v>
+        <v>507386</v>
       </c>
       <c r="R3" t="n">
-        <v>6985357</v>
+        <v>6985328</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,27 +853,18 @@
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -911,12 +886,7 @@
         <v>121078554</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,6 +996,223 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121078807</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Middagsberget, Middagsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>507467</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6985357</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121099245</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Middagsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>507503</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6985357</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2838-2026 artfynd.xlsx
+++ b/artfynd/A 2838-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121078567</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099286</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121078554</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121078807</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,8 +1238,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121099245</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>